--- a/StructureDefinition-Analysgrupp.xlsx
+++ b/StructureDefinition-Analysgrupp.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Analysgrupp.xlsx
+++ b/StructureDefinition-Analysgrupp.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Analysgrupp).</t>
+    <t>Klassen Analysgrupp grupperar ett antal analyser som utförs på ett eller flera prov från samma patient och som man väljer att betrakta som en enhet.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -254,6 +254,9 @@
     <t>Source attribute: namn</t>
   </si>
   <si>
+    <t>Angivelse av namn eller benämning på en analysgrupp</t>
+  </si>
+  <si>
     <t>Analysgrupp.listkod</t>
   </si>
   <si>
@@ -264,10 +267,16 @@
     <t>Source attribute: listkod</t>
   </si>
   <si>
+    <t>Kod för en analysgrupp.</t>
+  </si>
+  <si>
     <t>Analysgrupp.gruppkommentar</t>
   </si>
   <si>
     <t>Source attribute: gruppkommentar</t>
+  </si>
+  <si>
+    <t>Angivelse av kommentar för hela analysgruppen.</t>
   </si>
   <si>
     <t>Analysgrupp.bestarAv</t>
@@ -870,7 +879,7 @@
         <v>78</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -938,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -964,13 +973,13 @@
         <v>19</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1021,7 +1030,7 @@
         <v>19</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>71</v>
@@ -1038,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1067,10 +1076,10 @@
         <v>77</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1121,7 +1130,7 @@
         <v>19</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>71</v>
@@ -1138,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1164,13 +1173,13 @@
         <v>19</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1221,7 +1230,7 @@
         <v>19</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -1238,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1264,13 +1273,13 @@
         <v>19</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1321,7 +1330,7 @@
         <v>19</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
